--- a/Week-1/Ex4C_GTrends_marketing.xlsx
+++ b/Week-1/Ex4C_GTrends_marketing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimit\Documents\DataAnalytics\Week-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7DCD50FC-B946-4029-9CDC-654BC63FFD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95016B24-DAA6-4976-A641-1CAB31560440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{E2A75989-95A2-46C5-9E85-D438BEC300A5}"/>
   </bookViews>
@@ -23,10 +23,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">' by search term'!$A$1:$E$52</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2653,7 +2666,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C8C0964F-1464-4A96-A033-E09E699CF822}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C8C0964F-1464-4A96-A033-E09E699CF822}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
